--- a/stories/arbres/ATOM-EMO.LEX.004-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -823,6 +823,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -837,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1131,6 +1143,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1155,7 +1172,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam est dans la salle de bain avec papa. L'eau coule. Soudain, une goutte saute. Elle touche le nez d'Adam. Adam sent son cœur battre vite. Ses yeux s'ouvrent. Adam dit : je suis surpris. Être surpris, ce n'est pas honteux. Papa dit : d'abord respirer. Ensuite comprendre, avant d'agir. Adam souffle une grande fois. Il regarde le robinet. Il dit : je veux comprendre. C'est l'eau. Rien n'est cassé. Adam est content. Il partage un sourire. La joie est là. Plus tard, ils vont au parc. Une balle arrive près d'Adam. Adam sent encore le cœur. Il dit : je suis surpris. Il souffle. Il veut respirer. Il regarde. C'est la balle de Nino. Adam comprend. Il rend la balle. Il est content. Il invite Nino. La joie se partage. Dans la salle de bain, puis au parc, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
+          <t>Adam est dans la salle de bain avec papa. L'eau coule. Soudain, une goutte saute. Elle touche le nez d'Adam. Adam sent son cœur battre vite. Ses yeux s'ouvrent. Je suis surpris. Être surpris, ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Adam souffle une grande fois. Il regarde le robinet. Je veux comprendre. C'est l'eau. Rien n'est cassé. Adam est content. Il partage un sourire. La joie est là. Plus tard, ils vont au parc. Une balle arrive près d'Adam. Adam sent encore le cœur. Je suis surpris. Il souffle. Il veut respirer. Il regarde. C'est la balle de Nino. Adam comprend. Il rend la balle. Il est content. Il invite Nino. La joie se partage. Dans la salle de bain, puis au parc, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1293,6 +1310,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Adam est dans la salle de bain avec papa. L'eau coule. Soudain, une goutte saute. Elle touche le nez d'Adam. Adam sent son cœur battre vite. Ses yeux s'ouvrent.
+enfant-m|Je suis surpris. Être surpris, ce n'est pas honteux.
+papa|D'abord respirer. Ensuite comprendre, avant d'agir.
+narrateur|Adam souffle une grande fois. Il regarde le robinet.
+narrateur|Je veux comprendre. C'est l'eau. Rien n'est cassé.
+narrateur|Adam est content. Il partage un sourire. La joie est là. Plus tard, ils vont au parc. Une balle arrive près d'Adam. Adam sent encore le cœur.
+narrateur|Je suis surpris. Il souffle. Il veut respirer.
+narrateur|Il regarde. C'est la balle de Nino. Adam comprend. Il rend la balle. Il est content. Il invite Nino. La joie se partage. Dans la salle de bain, puis au parc, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1473,6 +1502,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Adam est surpris. Que fait-il d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1675,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a nommé : surpris. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1838,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Adam et Nino se passent la balle. Papa reste près.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2005,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-02.xlsx
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1148,6 +1148,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1322,6 +1327,11 @@
 narrateur|Il regarde. C'est la balle de Nino. Adam comprend. Il rend la balle. Il est content. Il invite Nino. La joie se partage. Dans la salle de bain, puis au parc, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1509,6 +1519,7 @@
           <t>narrateur|Adam est surpris. Que fait-il d'abord ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1680,6 +1691,7 @@
           <t>narrateur|Adam a nommé : surpris. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1855,7 @@
           <t>narrateur|Adam et Nino se passent la balle. Papa reste près.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.004-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adam est surpris deux fois</t>
+          <t>La goutte d'Amir</t>
         </is>
       </c>
     </row>
@@ -835,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une goutte saute sur le nez d'Amir. Il est surpris. Il souffle. Il comprend. Au parc, une balle arrive. Même geste. Il la rend à Nino.</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam est dans la salle de bain avec papa. L'eau coule. Soudain, une goutte saute. Elle touche le nez d'Adam. Adam sent son cœur battre vite. Ses yeux s'ouvrent. Je suis surpris. Être surpris, ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Adam souffle une grande fois. Il regarde le robinet. Je veux comprendre. C'est l'eau. Rien n'est cassé. Adam est content. Il partage un sourire. La joie est là. Plus tard, ils vont au parc. Une balle arrive près d'Adam. Adam sent encore le cœur. Je suis surpris. Il souffle. Il veut respirer. Il regarde. C'est la balle de Nino. Adam comprend. Il rend la balle. Il est content. Il invite Nino. La joie se partage. Dans la salle de bain, puis au parc, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
+          <t>Un savon canard attend au bord. Il est jaune et un peu mou. L'eau fait goutte, goutte. Les carreaux sont frais sous les pieds. La serviette a des petits bateaux. Le miroir est un peu flou. Une goutte glisse sur le carreau. Tu as vu le canard, Amir ? Il est mou. C'est le savon. On se lave les mains, tout doux. L'eau est tiède, tu vois ? En ce moment, l'eau coule. Elle est tiède sur les doigts. Soudain, une goutte saute. Elle touche le nez d'Amir. Amir sent son cœur battre vite. Ses yeux s'ouvrent. Je suis surpris. Tu es surpris. Ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Amir souffle une grande fois. Une buée s'ajoute au miroir. Tu veux comprendre ? Je veux comprendre. Il regarde le robinet. C'est l'eau. Oui. Rien n'est cassé. Je suis content. Tu partages un sourire. La joie est là. Plus tard, ils vont au parc. L'herbe sent le vert. Un banc est encore chaud. Une balle arrive près d'Amir. Elle roule vite dans l'herbe. Amir sent encore le cœur. Je suis surpris. Il souffle. Je veux respirer. Il regarde. C'est la balle de Nino. Tu as compris, avant d'agir. Bravo, Amir. Amir rend la balle. Nino, tiens. Nino la prend. Amir est content. Tu veux jouer ? La joie se partage. Dans la salle de bain, puis ici. On nomme : surpris. On respire. On cherche à comprendre. La balle fait un bruit mou dans l'herbe. Le savon canard attend encore à la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1317,14 +1329,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Adam est dans la salle de bain avec papa. L'eau coule. Soudain, une goutte saute. Elle touche le nez d'Adam. Adam sent son cœur battre vite. Ses yeux s'ouvrent.
-enfant-m|Je suis surpris. Être surpris, ce n'est pas honteux.
-papa|D'abord respirer. Ensuite comprendre, avant d'agir.
-narrateur|Adam souffle une grande fois. Il regarde le robinet.
-narrateur|Je veux comprendre. C'est l'eau. Rien n'est cassé.
-narrateur|Adam est content. Il partage un sourire. La joie est là. Plus tard, ils vont au parc. Une balle arrive près d'Adam. Adam sent encore le cœur.
-narrateur|Je suis surpris. Il souffle. Il veut respirer.
-narrateur|Il regarde. C'est la balle de Nino. Adam comprend. Il rend la balle. Il est content. Il invite Nino. La joie se partage. Dans la salle de bain, puis au parc, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.</t>
+          <t>narrateur|Un savon canard attend au bord.
+narrateur|Il est jaune et un peu mou.
+narrateur|L'eau fait goutte, goutte.
+narrateur|Les carreaux sont frais sous les pieds.
+narrateur|La serviette a des petits bateaux.
+narrateur|Le miroir est un peu flou.
+narrateur|Une goutte glisse sur le carreau.
+papa|Tu as vu le canard, Amir ?
+enfant-m|Il est mou.
+papa|C'est le savon.
+papa|On se lave les mains, tout doux.
+papa|L'eau est tiède, tu vois ?
+narrateur|En ce moment, l'eau coule.
+narrateur|Elle est tiède sur les doigts.
+narrateur|Soudain, une goutte saute.
+narrateur|Elle touche le nez d'Amir.
+narrateur|Amir sent son cœur battre vite.
+narrateur|Ses yeux s'ouvrent.
+enfant-m|Je suis surpris.
+papa|Tu es surpris.
+papa|Ce n'est pas honteux.
+papa|D'abord respirer.
+papa|Ensuite comprendre, avant d'agir.
+narrateur|Amir souffle une grande fois.
+narrateur|Une buée s'ajoute au miroir.
+papa|Tu veux comprendre ?
+enfant-m|Je veux comprendre.
+narrateur|Il regarde le robinet.
+enfant-m|C'est l'eau.
+papa|Oui.
+papa|Rien n'est cassé.
+enfant-m|Je suis content.
+papa|Tu partages un sourire.
+papa|La joie est là.
+narrateur|Plus tard, ils vont au parc.
+narrateur|L'herbe sent le vert.
+narrateur|Un banc est encore chaud.
+narrateur|Une balle arrive près d'Amir.
+narrateur|Elle roule vite dans l'herbe.
+narrateur|Amir sent encore le cœur.
+enfant-m|Je suis surpris.
+narrateur|Il souffle.
+enfant-m|Je veux respirer.
+narrateur|Il regarde.
+enfant-m|C'est la balle de Nino.
+papa|Tu as compris, avant d'agir.
+papa|Bravo, Amir.
+narrateur|Amir rend la balle.
+enfant-m|Nino, tiens.
+narrateur|Nino la prend.
+narrateur|Amir est content.
+enfant-m|Tu veux jouer ?
+narrateur|La joie se partage.
+papa|Dans la salle de bain, puis ici.
+papa|On nomme : surpris.
+papa|On respire.
+papa|On cherche à comprendre.
+narrateur|La balle fait un bruit mou dans l'herbe.
+narrateur|Le savon canard attend encore à la maison.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1356,7 +1419,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Adam est surpris. Que fait-il d'abord ?</t>
+          <t>Amir est surpris. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1516,7 +1579,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Adam est surpris. Que fait-il d'abord ?</t>
+          <t>narrateur|Amir est surpris.
+narrateur|Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1544,7 +1608,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam a nommé : surpris. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir.</t>
+          <t>Amir a encore l'herbe aux chaussettes. J'ai dit : je suis surpris. Deux fois. Tu as soufflé. Puis tu as voulu comprendre. Avant d'agir. Bravo, Amir. Tu as fait du bon travail. D'abord respirer. Oui. La balle attend entre Nino et lui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1688,7 +1752,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Adam a nommé : surpris. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir.</t>
+          <t>narrateur|Amir a encore l'herbe aux chaussettes.
+enfant-m|J'ai dit : je suis surpris.
+papa|Deux fois.
+papa|Tu as soufflé.
+papa|Puis tu as voulu comprendre.
+papa|Avant d'agir.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+enfant-m|D'abord respirer.
+papa|Oui.
+narrateur|La balle attend entre Nino et lui.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1716,7 +1790,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Adam et Nino se passent la balle. Papa reste près.</t>
+          <t>Amir et Nino se passent la balle. Papa reste près. On joue encore un peu ? Oui, papa. Tu as nommé : surpris. Tu as respiré. Tu as regardé. La balle est un peu humide d'herbe. Un oiseau crie, loin. C'était la balle de Nino. Oui. Tu as compris.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1852,7 +1926,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Adam et Nino se passent la balle. Papa reste près.</t>
+          <t>narrateur|Amir et Nino se passent la balle.
+narrateur|Papa reste près.
+papa|On joue encore un peu ?
+enfant-m|Oui, papa.
+papa|Tu as nommé : surpris.
+papa|Tu as respiré.
+papa|Tu as regardé.
+narrateur|La balle est un peu humide d'herbe.
+narrateur|Un oiseau crie, loin.
+enfant-m|C'était la balle de Nino.
+papa|Oui.
+papa|Tu as compris.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1880,7 +1965,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Amir. Tu as fait du bon travail. La balle s'arrête dans l'herbe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2020,7 +2105,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit : je suis surpris.
+enfant-m|J'ai soufflé.
+enfant-m|J'ai compris.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|La balle s'arrête dans l'herbe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2042,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2171,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-02.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam est dans la salle de bain avec papa. L'eau coule. Soudain, une goutte saute. Elle touche le nez d'Adam. Adam sent son cœur battre vite. Ses yeux s'ouvrent. Adam dit : je suis &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;. Être surpris, ce n'est pas honteux. Papa dit : d'abord respirer. Ensuite comprendre, avant d'agir. Adam souffle une grande fois. Il regarde le robinet. Il dit : je veux comprendre. C'est l'eau. Rien n'est cassé. Adam est content. Il partage un sourire. La joie est là. Plus tard, ils vont au parc. Une balle arrive près d'Adam. Adam sent encore le cœur. Il dit : je suis surpris. Il souffle. Il veut respirer. Il regarde. C'est la balle de Nino. Adam comprend. Il rend la balle. Il est content. Il invite Nino. La joie se partage. Dans la salle de bain, puis au parc, c'est pareil. On nomme : surpris. On respire. On cherche à comprendre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un savon canard attend au bord. Il est jaune et un peu mou. L'eau fait goutte, goutte. Les carreaux sont frais sous les pieds. La serviette a des petits bateaux. Le miroir est un peu flou. Une goutte glisse sur le carreau. Tu as vu le canard, Amir ? Il est mou. C'est le savon. On se lave les mains, tout doux. L'eau est tiède, tu vois ? En ce moment, l'eau coule. Elle est tiède sur les doigts. Soudain, une goutte saute. Elle touche le nez d'Amir. Amir sent son cœur battre vite. Ses yeux s'ouvrent. Je suis surpris. Tu es surpris. Ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Amir souffle une grande fois. Une buée s'ajoute au miroir. Tu veux comprendre ? Je veux comprendre. Il regarde le robinet. C'est l'eau. Oui. Rien n'est cassé. Je suis content. Tu partages un sourire. La joie est là. Plus tard, ils vont au parc. L'herbe sent le vert. Un banc est encore chaud. Une balle arrive près d'Amir. Elle roule vite dans l'herbe. Amir sent encore le cœur. Je suis surpris. Il souffle. Je veux respirer. Il regarde. C'est la balle de Nino. Tu as compris, avant d'agir. Bravo, Amir. Amir rend la balle. Nino, tiens. Nino la prend. Amir est content. Tu veux jouer ? La joie se partage. Dans la salle de bain, puis ici. On nomme : surpris. On respire. On cherche à comprendre. La balle fait un bruit mou dans l'herbe. Le savon canard attend encore à la maison.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam est &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;. Que fait-il d'abord ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir est surpris. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1583,7 +1583,6 @@
 narrateur|Que fait-il d'abord ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1608,12 +1607,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a encore l'herbe aux chaussettes. J'ai dit : je suis surpris. Deux fois. Tu as soufflé. Puis tu as voulu comprendre. Avant d'agir. Bravo, Amir. Tu as fait du bon travail. D'abord respirer. Oui. La balle attend entre Nino et lui.</t>
+          <t>Amir a encore l'herbe aux chaussettes. J'ai dit : je suis surpris. Deux fois. Tu as soufflé. Puis tu as voulu comprendre. Avant d'agir. Bravo, Amir. D'abord respirer. Oui. La balle attend entre Nino et lui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam a nommé : &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;. Deux fois. Il a soufflé. Il a voulu comprendre avant d'agir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a encore l'herbe aux chaussettes. J'ai dit : je suis surpris. Deux fois. Tu as soufflé. Puis tu as voulu comprendre. Avant d'agir. Bravo, Amir. D'abord respirer. Oui. La balle attend entre Nino et lui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1759,13 +1758,11 @@
 papa|Puis tu as voulu comprendre.
 papa|Avant d'agir.
 papa|Bravo, Amir.
-papa|Tu as fait du bon travail.
 enfant-m|D'abord respirer.
 papa|Oui.
 narrateur|La balle attend entre Nino et lui.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,7 +1792,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam et Nino se passent la balle. Papa reste près.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir et Nino se passent la balle. Papa reste près. On joue encore un peu ? Oui, papa. Tu as nommé : surpris. Tu as respiré. Tu as regardé. La balle est un peu humide d'herbe. Un oiseau crie, loin. C'était la balle de Nino. Oui. Tu as compris.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1940,7 +1937,6 @@
 papa|Tu as compris.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Amir. Tu as fait du bon travail. La balle s'arrête dans l'herbe. L'histoire est finie.</t>
+          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Amir. La balle s'arrête dans l'herbe.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Amir. La balle s'arrête dans l'herbe.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2109,12 +2105,9 @@
 enfant-m|J'ai soufflé.
 enfant-m|J'ai compris.
 papa|Bravo, Amir.
-papa|Tu as fait du bon travail.
-narrateur|La balle s'arrête dans l'herbe.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La balle s'arrête dans l'herbe.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2171,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-02.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adam, papa, Nino</t>
+          <t>Amir, papa, Nino</t>
         </is>
       </c>
     </row>
